--- a/光伏配储项目/电价数据/2026/董塘站.xlsx
+++ b/光伏配储项目/电价数据/2026/董塘站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.51255</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38473</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.7691</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.59756</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5844400000000001</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.51446</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.52722</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43785</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45471</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.42692</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42216</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.76342</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.43036</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.41876</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39661</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38507</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40125</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.4234</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41279</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35418</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39167</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38512</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41715</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39227</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.4209</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41411</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42411</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41211</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44291</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30003</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.27444</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29986</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30702</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.31317</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>-0.03786</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>-0.04017</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>-0.04207</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>-0.03724</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>-0.03351</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>-0.03546</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>-0.023</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.02567</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.02478</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>-0.049</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.04911</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.01808</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.01333</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>-0.0271</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.01816</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>-0.03986</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>-0.04720000000000001</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>-0.03777</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>-0.007860000000000001</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.20019</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.28444</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.55621</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.4296</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.39878</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.67863</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39573</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.56916</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43363</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43759</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.42462</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.56608</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.44941</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.6039</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.7988099999999999</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.6273099999999999</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.6314299999999999</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.73897</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.9293899999999999</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.41441</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.65964</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.58331</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.72296</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.47294</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.37715</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.6239199999999999</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.6036900000000001</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.5004</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48061</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.44342</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41627</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42599</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.69177</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0.99878</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.63673</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.54634</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.6659299999999999</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.49348</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5174500000000001</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50461</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50493</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48684</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.4689</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37887</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37957</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.38994</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33652</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.36971</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35516</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35475</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37404</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.3743</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35825</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37931</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41774</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.48429</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.55157</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.48988</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.42804</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.36621</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34786</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.34845</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.42821</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.45126</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.26768</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.32976</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35104</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.24551</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.18953</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.17452</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.30195</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.11015</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.19585</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.23534</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.01541</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.16245</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>-0.0399</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.02763</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.13524</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.19665</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.18471</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.37426</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>-0.01411</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.01949</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>-0.04198</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.36271</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>-0.03593</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.33728</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.31858</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.36244</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.37613</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.41683</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.45167</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.43225</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.43574</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.42462</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.4024</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.5842000000000001</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.48351</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.3434</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.493</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.5879</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.5326799999999999</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.67155</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.63224</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.7193999999999999</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.43765</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.40968</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.7657</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.47138</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.33152</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.46317</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.35438</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.43568</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.44258</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.43575</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42923</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.4034700000000001</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.32288</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.3764</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35523</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33471</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.50983</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.34183</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.42745</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.39579</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.423</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.4093</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.37185</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38993</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38379</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36391</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42933</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44501</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33611</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37067</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39649</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.3678</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36858</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36173</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35213</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36715</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35936</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38531</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39638</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47376</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44522</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43952</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34765</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39533</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35307</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36747</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34767</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.26118</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.25987</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.25269</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.32864</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.20894</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.23362</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.27187</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.31922</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.32706</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.32195</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.33413</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.34563</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.34938</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.34268</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.41261</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.32578</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.36755</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.4425</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.41807</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.37163</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.4192</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.44217</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.47242</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.50758</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.4097</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.3138</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.34151</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.34798</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.3556</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.36459</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.45804</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.4083</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.46306</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.39599</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.45185</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.5254800000000001</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.3715</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.38136</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.5255700000000001</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.6088300000000001</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.57733</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.59616</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.33095</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.46383</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.42259</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.48218</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.40252</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.44735</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.43644</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.45858</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.44414</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.39531</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.37446</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.41982</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.39939</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.39522</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39869</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36248</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.3487</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34207</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.47768</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.34191</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38764</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38892</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.39688</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36617</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35807</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38462</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38369</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.35827</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.45012</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35762</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34734</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36003</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35556</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35628</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33638</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33358</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.32938</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33297</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.32921</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.34922</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33921</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35152</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38303</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38911</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34518</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37236</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34311</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39178</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.3621</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.36644</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.34263</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.26088</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34037</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.1249</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.24127</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.19806</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.28226</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.20107</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.30436</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.56025</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.32946</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.40189</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.31357</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.2149</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.22762</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.16917</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>-0.02252</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.03465</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>-0.00102</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.23797</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.01374</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>-0.02603</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.10195</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.19409</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.19458</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.10233</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.10141</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.10208</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.33626</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.16453</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.32296</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.32183</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.33198</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33791</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.3739</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.36092</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.35353</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.39916</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.44621</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.3444700000000001</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.39302</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.39225</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.38973</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.41514</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.34103</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.35887</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.3405899999999999</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31916</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32335</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29368</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.30757</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31553</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31167</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.31605</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.30353</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.3433</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.3822</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35549</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33908</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.31866</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31677</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.31946</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31694</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31394</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31535</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31558</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.3044</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.3085</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.30195</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30379</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30628</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31362</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33261</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.30547</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.29993</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.21433</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.22332</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.21513</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.20933</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04474</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.22018</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.21622</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.19439</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.02873</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.18172</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.09594</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.03338</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.03386</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.03592</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.03793999999999999</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.03565</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04225</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04686</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.04092</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04079</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.03824</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>-0.04643</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>-0.03796</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05797</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.01015</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.03404</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.09594</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29012</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29181</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31547</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.3358</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33592</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.3876</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39196</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38735</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37687</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39933</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39977</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40962</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46715</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35449</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39606</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.39954</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.4167</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35493</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35805</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34473</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35503</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35076</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36797</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.6535</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.39952</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44493</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42224</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42212</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.3597</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35848</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33185</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30874</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35123</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33484</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31419</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.32954</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32158</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29992</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32148</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33514</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33827</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34162</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31573</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10252</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04343</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04699</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04482</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.044</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.33392</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01181</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20964</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.05097</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04396</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04575</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04563</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04371</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04337</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04550999999999999</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04341</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04527</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04539</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.0436</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04424</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.02249</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.00376</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04472</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04740999999999999</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04793</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19972</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14271</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28991</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29463</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30451</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.2998</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.2949</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.2928</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29326</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29222</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29675</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29072</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29495</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26873</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29379</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30853</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30372</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.3022</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31432</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31836</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34753</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34424</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36613</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36467</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33529</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31698</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31033</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40415</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34971</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30701</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31461</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30132</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28112</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29439</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29066</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28081</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27114</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27087</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28101</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17235</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15859</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.1709</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14768</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15942</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15856</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23609</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21398</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22649</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.2688</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28563</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29073</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29067</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28081</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28101</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28041</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27071</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28089</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32233</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31013</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.3049</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31627</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30937</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35893</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29749</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38362</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42819</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45649</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41851</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41535</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38885</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40247</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.2993</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15653</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29438</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31095</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31344</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31274</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34631</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38547</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49798</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9140900000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86252</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29602</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.3533</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88715</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63154</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18674</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8684700000000001</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.53577</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.3305</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03267</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53043</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7906799999999999</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5295599999999999</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77267</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7773</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87673</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87371</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49287</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.3984</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39953</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44962</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20663</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87881</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55101</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62149</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53823</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49758</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45577</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42421</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43708</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.4499</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38808</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45267</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41976</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35165</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39989</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36511</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38482</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41453</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43348</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34369</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39004</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33822</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33139</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34459</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40211</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34726</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45068</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35337</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39986</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.39951</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58539</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.427</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59556</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60114</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.6900700000000001</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46854</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.41747</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.58014</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.41375</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.44751</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.33544</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.85942</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.78971</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.79915</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.2614</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.44036</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.32758</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33303</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30563</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.30065</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.54604</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.35933</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.26714</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31058</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33271</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33675</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33709</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31786</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30624</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31509</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31489</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32017</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30346</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29555</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31354</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31207</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31433</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.30982</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31472</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32293</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32433</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35413</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34027</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34008</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33796</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33026</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.3371499999999999</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33516</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.40944</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41206</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45159</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.4144</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39108</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37455</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35328</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.918</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36017</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46445</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.42137</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.40762</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.46357</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38028</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40932</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.36032</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38881</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35888</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34543</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32277</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.39952</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.49901</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38716</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34324</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35493</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37026</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35768</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36278</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31635</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31358</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33252</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33783</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31491</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31284</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29063</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31241</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.29073</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.29755</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16621</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30447</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.33198</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.31713</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.33565</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.30676</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26221</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.1989</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27721</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.19287</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31118</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28321</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31141</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31179</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35271</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.09168000000000001</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31444</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31144</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.32125</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.30306</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.31161</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29992</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30912</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32034</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31399</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29001</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34802</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.2556</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.34971</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32178</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.33682</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.33719</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27645</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32884</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.30983</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.3372</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38521</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.44282</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.34976</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.38672</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42316</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35244</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44982</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.3385</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.4199</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35877</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40114</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.39984</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.595</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.34928</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.8896499999999999</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.45548</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.1605</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.6997899999999999</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79061</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.66422</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.57888</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.4496</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45058</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50095</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.44015</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43737</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41519</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41309</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42343</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.50019</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41309</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43432</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.4126</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43445</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39053</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42767</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45001</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39642</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42372</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43376</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41309</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41313</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.39997</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42314</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39876</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40235</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.36282</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.34507</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29627</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.36659</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.36859</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.34186</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30754</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.31739</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30369</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.55059</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.36369</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.30796</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24965</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.30208</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.15641</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.27833</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27553</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.01085</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.33755</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30117</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26158</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25527</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30714</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28506</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.2904</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.2918</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.30962</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31369</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.32387</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.3289</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31559</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.34003</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.34037</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.40354</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.40025</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.35079</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.34001</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.36805</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.34131</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.3621</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.36452</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36216</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34887</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.56977</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46197</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.8466</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46421</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.4362</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37733</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.45765</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38512</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36817</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33316</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.33966</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32834</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32329</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42151</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.3428</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.3242</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32747</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.3242</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32299</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32601</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32454</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.3186</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31467</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.31828</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.31822</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30912</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32407</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31013</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.31879</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.38962</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32193</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34826</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39785</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37302</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34864</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33766</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35345</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33354</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.28096</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.30899</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.29455</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.27934</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.22554</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.14157</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.14519</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.27994</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.1528</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>-0.01564</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.00584</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14131</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.13615</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.24727</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.13668</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.18201</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.03755</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>-0.00783</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>-0.02416</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.10783</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.1074</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.1263</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.13581</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.1407</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.27638</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.32482</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.32027</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.3439</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.35558</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.34706</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.36407</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34284</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37906</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39712</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38391</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.44841</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39876</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.38972</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40046</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39624</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.45119</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.4384</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43773</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44264</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44368</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38982</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.397</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39083</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35854</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.35911</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34668</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34816</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33861</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5369400000000001</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38841</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46745</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42269</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41483</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.36974</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.3805</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.37885</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37927</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36984</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.37999</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39079</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.36995</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.37992</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.34989</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34693</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35484</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.3445</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34488</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34452</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35443</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.36992</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38001</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32776</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34186</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34862</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.36075</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29791</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31425</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31374</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30853</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29517</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.17742</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.16132</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.03904</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.2007</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30924</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.17967</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.2433</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.04284</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29602</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28858</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31245</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.35434</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31364</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29397</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.28656</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24221</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31544</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30794</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.3259</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30633</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28579</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.32486</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.34153</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33951</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32718</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.32753</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34222</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35164</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34516</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.35328</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36687</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.4040899999999999</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.38136</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.37192</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.25967</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.34175</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38025</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.3558</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35727</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35474</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41484</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.32021</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36694</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.36925</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.3797</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38017</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38482</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.3496</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.35984</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.33984</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36546</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41706</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37027</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39078</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35204</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.35939</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.3511</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34123</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34718</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34522</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34909</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34637</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34907</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34262</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.3415</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34261</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33806</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33937</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33258</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34024</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.34254</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34953</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34779</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36168</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.35212</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33865</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33403</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32392</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.30947</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.39357</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.36391</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.39438</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.43494</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.33484</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.4257</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.34988</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.39148</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.36981</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.52528</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.24946</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.27398</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.21197</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.2856</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.47415</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.30332</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.28857</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.30113</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.3136</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.31082</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.31029</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.45806</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.3581</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.3436</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.34142</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.34801</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.35285</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.3157</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.40589</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32503</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.32565</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.43453</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.41678</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.6898300000000001</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36218</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.36529</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.32794</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.33175</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.31858</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.50986</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.22205</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.37886</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30178</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31081</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32602</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.33188</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.3135</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.31247</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.31531</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.32871</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.39677</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.34988</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33914</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.33483</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.32178</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32751</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.34223</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32662</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32674</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.3265</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32688</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33001</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32492</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32009</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31968</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32285</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32599</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.32975</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33434</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34502</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.33943</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33386</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.33092</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33417</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34343</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.3479100000000001</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32816</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.33234</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32445</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.34111</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.1798</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34452</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.21621</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.29826</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.2834</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.30143</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.17394</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.21056</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.23752</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.23811</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33438</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.29886</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.31657</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32732</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31965</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.23738</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.30015</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.30567</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.31306</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.3146</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36375</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.34164</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.3445299999999999</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.3498</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.34979</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.35955</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.32973</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.33658</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.35043</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.3434700000000001</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.33535</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.34133</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.33654</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.3469</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.35144</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.35366</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38521</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37149</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.38683</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35484</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37933</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.34802</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.34922</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.34988</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34869</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34948</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33931</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34911</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35118</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34905</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34921</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34606</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.35769</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34685</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34199</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34909</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33669</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33939</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33929</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36876</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32421</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33939</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34908</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33636</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34487</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33559</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34911</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34911</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33615</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.3398</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32801</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34818</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33633</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30869</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32624</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32824</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.21303</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31296</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.07751000000000001</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.07123</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.07486</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.07818000000000001</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32548</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.05148</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.04917</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.09287999999999999</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.07626000000000001</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.07576999999999999</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.07740000000000001</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.01881</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.07709000000000001</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.07965000000000001</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32973</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.30804</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.07679000000000001</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.07944</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.2122</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.29807</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33725</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34495</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35865</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.35514</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35371</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35445</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36616</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34967</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.35931</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34557</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.35858</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35858</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36063</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34853</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37845</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38046</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38428</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.41629</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41133</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37905</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.3755</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65638</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.7697000000000001</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.45167</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.28087</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45738</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35245</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35903</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33946</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.3442</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32209</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41091</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37607</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37059</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36182</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35864</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.3618</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35786</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35876</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35262</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35589</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35187</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34749</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37019</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35857</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35631</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37853</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36567</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37967</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35636</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35627</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35098</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35167</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35768</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34927</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32967</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.31927</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33139</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32565</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26553</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.14848</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.06937</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.06286</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.06324</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19986</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.05506</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.27991</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.30942</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.28033</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.21642</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.25551</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28497</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.27722</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28946</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.2899</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30438</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.31136</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32159</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.23024</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29789</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.29283</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34513</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.33772</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33169</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.33236</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.34752</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.31591</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33335</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.3624</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.34838</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.35965</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31879</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.4323</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.38163</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.41354</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.63961</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.59721</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.60489</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.48496</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.8100700000000001</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.48726</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.8120299999999999</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.44206</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.48914</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40028</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.36392</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.35298</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.47034</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.42981</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41847</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37818</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37461</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36693</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.35981</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.48844</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.5268699999999999</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.47943</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.48217</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41615</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.3967</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40219</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.40943</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40743</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41571</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39824</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39435</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.38842</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.4079</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.38468</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.36956</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.38948</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38754</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41637</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.38994</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.39946</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.39954</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.3708</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.38611</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.38379</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.38784</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.41404</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.38794</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.37088</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.38476</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.36883</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.37107</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.34709</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.09765</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.41007</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.44663</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.43869</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.16675</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.13411</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.06825000000000001</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.08311</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.09204999999999999</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.10965</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.05347</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.21751</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.22892</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.08678</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>-0.00254</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.04015</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.04097</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.08506</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.02822</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.01822</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.09859999999999999</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.00105</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.02401</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.02783</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.01566</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.01946</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.01748</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.01071</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.009380000000000001</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.04338</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.00604</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.01311</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.2437</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.24335</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.34192</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35307</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.35071</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33795</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.37394</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.43602</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.49185</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.5012300000000001</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.50463</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.5424099999999999</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.6900299999999999</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.7112000000000001</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.92018</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.52827</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.80599</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.5822200000000001</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.5248999999999999</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.8312200000000001</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.77013</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6234400000000001</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.67215</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.4414</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.47164</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.48163</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47608</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.46884</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41668</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.5511</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42736</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44107</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45497</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43406</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42401</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44483</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41574</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.39851</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45388</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39683</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.4039</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39584</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38552</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37748</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37257</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35666</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36564</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37402</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37055</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.35964</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35952</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36564</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38557</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.38951</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37918</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36579</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36105</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35482</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.36602</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.2914</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.26306</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.30135</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.29864</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.34226</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.2845299999999999</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.28962</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.24226</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.08089</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.02172</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.10494</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.19742</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.09928000000000001</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.05774</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.04556</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.04117</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.0301</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.0257</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.06697</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.04525999999999999</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.07708</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.03358</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.0322</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.02242</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.0745</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.07279000000000001</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.10278</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.0871</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.23995</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.25103</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.25154</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.26014</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.33418</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.33308</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.36425</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.39067</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.3703</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.43286</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41574</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41487</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38367</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.37687</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38555</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.39073</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40871</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40922</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.3454700000000001</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.37104</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37589</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39599</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37879</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35486</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39905</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.37906</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37452</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.35874</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39463</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37976</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36505</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.32864</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44373</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36104</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.39741</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.3927</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.3559</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37827</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.34921</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37634</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35597</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35661</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35321</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.34906</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34525</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34825</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.33932</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33417</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.33916</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34415</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.32914</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.32715</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.32704</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33523</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.3169</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.31582</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31302</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.30721</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.25714</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.27476</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.27142</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.27221</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22566</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.26241</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.22987</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.23335</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.2492</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.22985</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.13941</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.25989</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.23486</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.23657</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.05062</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04305</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25007</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.23331</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.16936</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18749</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.24039</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31311</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30121</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.23383</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.23801</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.213</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.03517</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.20532</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.21384</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.19232</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.23091</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.23648</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.19439</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.23821</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.23871</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35254</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.34404</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.31866</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.32993</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.383</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.35361</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.33778</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35411</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.34922</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.35144</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.34623</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.3638</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.35842</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.3683999999999999</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36328</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37801</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.35812</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.35278</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.35781</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34656</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34558</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34684</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.34049</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32485</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.3364</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34229</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33722</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.3257</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32132</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31669</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.30417</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.30703</v>
+      </c>
+      <c r="N136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.22413</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.21667</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.21669</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.30003</v>
+      </c>
+      <c r="S136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.29613</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.29613</v>
+      </c>
+      <c r="V136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.22374</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.29503</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.29613</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.29652</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.29988</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.27963</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.20556</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.19331</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>-0.04944</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.04945</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04946</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>-0.04987</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.04952</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.04945</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04948</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.03867</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04142</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.03895000000000001</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04828</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04786</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.04720000000000001</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.03856</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.0495</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04948</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04949</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04928</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.00067</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.25238</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04953</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04925</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04949</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.04642</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.02164</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04947</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04945</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03774</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.19017</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.24797</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.2756</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27981</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.30103</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.30475</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.32334</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.21432</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.22631</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.33394</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.21412</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.21282</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.24826</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.22564</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.22568</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.3062</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.37919</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.32552</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.33984</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.32063</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.30114</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.31842</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.29894</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.29555</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.13871</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.22698</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.54014</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.22352</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.26642</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.40541</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.35091</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.25429</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.3338</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.30384</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.2781</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.31394</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.29214</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.28868</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.28574</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.28908</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.27556</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.29201</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.27046</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.26736</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.2947</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.31003</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.28423</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.29473</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.28999</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.33474</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.10185</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.34328</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.31073</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.30508</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.2704</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.2606</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.6307200000000001</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.76347</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.75398</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.5806399999999999</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.23426</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.30653</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>-0.02608</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.22687</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.17868</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.20169</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.20091</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.17586</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.04902</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.03574</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.07940000000000001</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.00188</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.01991</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.04234</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>-0.00363</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.04271</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>-0.00258</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.20967</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.2095</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.01592</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.18134</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.19339</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.18843</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.16173</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25654</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.2354</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.26309</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.27806</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.28228</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.30795</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32497</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33537</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33211</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33587</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32914</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35463</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.33928</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.36688</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.32474</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.3758</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.36452</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.424</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.36356</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.36769</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.35278</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.36094</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.3523</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36856</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.35425</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.36442</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.36345</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.32386</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.31958</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32733</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.3281</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32811</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33675</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32152</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.35647</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.29604</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.3655</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.37906</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.37302</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.37304</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.35997</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.36125</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.33954</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.34638</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32587</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34178</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.16379</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.33363</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32344</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.32086</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.32732</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.32648</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.33172</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33691</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.34251</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.5199</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.53107</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.37299</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.33555</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.29825</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.41981</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.41726</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.36085</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.25874</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.26559</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.20891</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.37643</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.09376000000000001</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.04702000000000001</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.12002</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.04597</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.07840999999999999</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.08499</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.24663</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31142</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.14176</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.27685</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.27025</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30545</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.24796</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32596</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.30105</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.32377</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.29493</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.30455</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.21536</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.23521</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.2445</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.2412</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.31125</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.31005</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.30007</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.30055</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.33559</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.35348</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35615</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.35855</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.35859</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.35536</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33577</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34881</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.38205</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36324</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.37818</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.41571</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.33961</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.40065</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.34807</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.36913</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.35597</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.35623</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36274</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.42131</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.35054</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.35204</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.33725</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.34417</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.34007</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.82404</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.38785</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.39276</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.3747200000000001</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.35804</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.35338</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.39384</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.35227</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.37837</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.35421</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.34684</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35457</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.34902</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.33326</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33156</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33787</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.35167</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.33808</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36735</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.37597</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36777</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35801</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.36042</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.35668</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.36309</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.33366</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.5375</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.34291</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.41746</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.27762</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.37855</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.32922</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.36468</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.32985</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.24788</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.24199</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.24675</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.21949</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.30115</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.22329</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.0697</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.09011</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.08401</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.24662</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.06129</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.08934</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.21417</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.21379</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.21638</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.08891</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.08247</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.09007</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.08899</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.09053</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.08095000000000001</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.20751</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.09719</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.26049</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.25731</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.2987</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.34544</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.45027</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.34772</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.46758</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.36683</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.39276</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.41407</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.3582</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.45198</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.37161</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.37203</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.38212</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.37238</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.41424</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.35389</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.36813</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.36179</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.39046</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.37259</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.36448</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.37585</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.36838</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.2746499999999999</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.33705</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.3355</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.31573</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.40202</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.3733399999999999</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.37426</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.37005</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.3484</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.35887</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.36385</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.36434</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.36498</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.36458</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36175</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.32216</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35862</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.33298</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.32459</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.31542</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.32481</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.32273</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.21163</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.32164</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.29864</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.3582</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.29708</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.37111</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.29684</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.09566</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.25486</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.29852</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.25489</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.2115</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.24926</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.24739</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.26297</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.29924</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.4472</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.38996</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.37167</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.24453</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.24837</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.07728</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.21921</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.07291</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.10114</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.09704</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.09748999999999999</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.21299</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.24541</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.08094</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33765</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.31548</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.07278</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.08766</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.09211</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.07993</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.22149</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.25687</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.25011</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.24149</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.09952</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.22594</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.27121</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.3407</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.11133</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36866</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.25684</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.31032</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.34288</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.3085</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.39094</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.39148</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.42403</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.44424</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.43835</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.40688</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.41981</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.44614</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.41836</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.4572</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.41382</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.39103</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.45017</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.45114</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.7445499999999999</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.44305</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.42322</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.37236</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.38742</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.37204</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.34301</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.36329</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.34206</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.23306</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36228</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.34569</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.35876</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.34338</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33234</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.33263</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.31126</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.29645</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.3428</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.31366</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.31044</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.32279</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.31319</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.31844</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.23842</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.27513</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.29494</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.08069</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.30216</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.23752</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.23673</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.24371</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.3096</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.31115</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.31658</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.31965</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.31101</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.24637</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.29782</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.24287</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.23779</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.25411</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.07454000000000001</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.08981</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.24407</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.27388</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.24001</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.22015</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.03607</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.07006</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.21544</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.00464</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.23658</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.34506</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.05714</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.10219</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.05243</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.02531</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.01864</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.30201</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.26341</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.03346</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>-0.00341</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.02978</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.04012</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.22974</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.08737</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.01748</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.04848</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.03793</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.03999</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.08964</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.09264</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.09683</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.09326999999999999</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.25833</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.26055</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.10532</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.11252</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.2291</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.21736</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.24721</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.33232</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.24931</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.26766</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.3083399999999999</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.3798</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.38968</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.38944</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.35489</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.39185</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.36738</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.37762</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.33669</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.35342</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.37423</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.30669</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.34233</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.34589</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.24668</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.24532</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.24049</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.20137</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.24039</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.24006</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.55508</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.39142</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.45985</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.24137</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.34611</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.32231</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.37018</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.34777</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.33883</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34787</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.32105</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.31875</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.31265</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.32624</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.23878</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.31661</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.29752</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.33617</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.33718</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.32546</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.3115</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.32082</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.24616</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.24369</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.23746</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.23933</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.08758000000000001</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.09420000000000001</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.25418</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.22213</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.04941</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.08974</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.08649999999999999</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.36569</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.24631</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.21562</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.03538</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.11358</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.04858</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.08076999999999999</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.0446</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>-0.02275</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.05376</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>-0.0151</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.0129</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.10735</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>-0.008320000000000001</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.2591</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.30525</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.26179</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.25575</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.32959</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.31947</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.3034</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.32396</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.36855</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.35471</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.38184</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36182</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.3723</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39033</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36457</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.38202</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.49568</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.37717</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.37514</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.37694</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.3819</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.36132</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.38284</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.34472</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.36036</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.36404</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.24676</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.32599</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.33918</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35631</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.33316</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.30699</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.37891</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.37888</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37577</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.37333</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.31551</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.2982</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.33606</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.33497</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.3439</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34454</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.3436</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.34728</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33856</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33366</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35199</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.34602</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.33591</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.34474</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.3526</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34768</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.29816</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.08055</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.24049</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.21192</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.23888</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.23894</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.06667000000000001</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.21925</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.03904</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.01875</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.24342</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.22746</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.23116</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.13545</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.02402</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>-0.00627</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>-0.00294</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>-0.04944</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.01493</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>-0.01252</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>-0.00404</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.08126</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.33123</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.14367</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.01718</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>-0.00327</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>-0.00104</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.31096</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.00653</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>-0.00912</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>-0.01506</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>-0.02345</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>-0.00174</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.22179</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.24523</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.03811</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.22034</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.22118</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.23779</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.24097</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.23936</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.24022</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.30452</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.25207</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.33173</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.34716</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.34776</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.34738</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.36425</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.37999</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.35533</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37117</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.37458</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.38475</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.40152</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.47466</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.38934</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.39057</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.38331</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.38763</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.37082</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.37986</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.38549</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.37725</v>
       </c>
     </row>
   </sheetData>
